--- a/data/food-images/delicacies_database.xlsx
+++ b/data/food-images/delicacies_database.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\win10-g9\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\FirstBite\firstbite-server\data\food-images\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42340519-5A79-442C-9659-1EB49A2C53B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4177599E-477D-4FBD-8A2C-73872309876E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="156" yWindow="24" windowWidth="11760" windowHeight="12156" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10896" yWindow="252" windowWidth="11760" windowHeight="12156" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="497">
   <si>
     <t>FirstBite 음식 DB 입력 템플릿</t>
   </si>
@@ -912,12 +912,6 @@
     <t>ease_score</t>
   </si>
   <si>
-    <t>price_min_krw</t>
-  </si>
-  <si>
-    <t>price_max_krw</t>
-  </si>
-  <si>
     <t>recommendation_reason</t>
   </si>
   <si>
@@ -1489,6 +1483,170 @@
   </si>
   <si>
     <t>풋콩 50g, 무염 대표값</t>
+  </si>
+  <si>
+    <t>estimated_price</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>원</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>500</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>원</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>원</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1,600</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>원</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>3,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>원</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1,300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>원</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1,500</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>원</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>원</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2,700</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>원</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1,100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>원</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1500,7 +1658,7 @@
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="178" formatCode="0.0"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1579,6 +1737,13 @@
       <color rgb="FF1F1F1F"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F2937"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -1638,7 +1803,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1674,12 +1839,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1715,9 +1895,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1761,12 +1938,369 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+      <extLst>
+        <x:ext xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </extLst>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="15">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1860,31 +2394,30 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="SideMenuCatalogTable" displayName="SideMenuCatalogTable" ref="A1:U16" totalsRowShown="0">
-  <tableColumns count="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="SideMenuCatalogTable" displayName="SideMenuCatalogTable" ref="A1:T16" totalsRowShown="0">
+  <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="food_code"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="food_name"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="serving_description"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="serving_amount"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="serving_unit"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="carb_g"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="fiber_g"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="protein_g"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="fat_g"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="available_carb_g"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="gi">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="serving_unit" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="carb_g" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="fiber_g" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="protein_g" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="fat_g" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="available_carb_g" dataDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="gi" dataDxfId="8">
       <calculatedColumnFormula>IFERROR(INDEX(foods!$N:$N,MATCH(B2,foods!$B:$B,0)),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="gl"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0300-00000E000000}" name="calorie_kcal"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0300-00000F000000}" name="focus_nutrient"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0300-000010000000}" name="purchase_place"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0300-000011000000}" name="ease_score"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0300-000012000000}" name="price_min_krw"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0300-000013000000}" name="price_max_krw"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0300-000014000000}" name="recommendation_reason"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0300-000015000000}" name="is_active"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="gl" dataDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0300-00000E000000}" name="calorie_kcal" dataDxfId="6"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0300-00000F000000}" name="focus_nutrient" dataDxfId="5"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0300-000010000000}" name="purchase_place" dataDxfId="4"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0300-000011000000}" name="ease_score" dataDxfId="3"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0300-000012000000}" name="estimated_price" dataDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0300-000014000000}" name="recommendation_reason" dataDxfId="1"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0300-000015000000}" name="is_active" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2107,10 +2640,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="26.85" customHeight="1">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
+      <c r="B1" s="28"/>
     </row>
     <row r="2" spans="1:2" ht="21.75" customHeight="1">
       <c r="A2" s="4" t="s">
@@ -2178,26 +2711,26 @@
     </row>
     <row r="10" spans="1:2" ht="28.8" customHeight="1">
       <c r="A10" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="28.8" customHeight="1">
+      <c r="A11" s="21" t="s">
         <v>360</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B11" s="22" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="28.8" customHeight="1">
-      <c r="A11" s="22" t="s">
+    <row r="12" spans="1:2" ht="38.4" customHeight="1">
+      <c r="A12" s="26" t="s">
         <v>362</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B12" s="26" t="s">
         <v>363</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="38.4" customHeight="1">
-      <c r="A12" s="27" t="s">
-        <v>364</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -2305,20 +2838,20 @@
       <c r="U1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="V1" s="18" t="s">
+      <c r="V1" s="17" t="s">
+        <v>364</v>
+      </c>
+      <c r="W1" s="17" t="s">
+        <v>312</v>
+      </c>
+      <c r="X1" s="17" t="s">
+        <v>365</v>
+      </c>
+      <c r="Y1" s="23" t="s">
         <v>366</v>
       </c>
-      <c r="W1" s="18" t="s">
-        <v>314</v>
-      </c>
-      <c r="X1" s="18" t="s">
+      <c r="Z1" s="23" t="s">
         <v>367</v>
-      </c>
-      <c r="Y1" s="24" t="s">
-        <v>368</v>
-      </c>
-      <c r="Z1" s="24" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="2" spans="1:26" ht="13.95" customHeight="1">
@@ -2360,7 +2893,7 @@
         <f t="shared" ref="M2:M33" si="0">IF(OR(I2="",J2=""),"",MAX(I2-J2,0))</f>
         <v>66.099999999999994</v>
       </c>
-      <c r="N2" s="13">
+      <c r="N2" s="12">
         <v>90</v>
       </c>
       <c r="O2" s="6">
@@ -2370,7 +2903,7 @@
       <c r="P2" s="8">
         <v>322</v>
       </c>
-      <c r="Q2" s="17" t="s">
+      <c r="Q2" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R2" s="1" t="s">
@@ -2381,18 +2914,18 @@
       </c>
       <c r="T2" s="9"/>
       <c r="U2" s="9"/>
-      <c r="V2" s="19"/>
-      <c r="W2" s="20" t="s">
+      <c r="V2" s="18"/>
+      <c r="W2" s="19" t="s">
+        <v>368</v>
+      </c>
+      <c r="X2" s="24">
+        <v>706</v>
+      </c>
+      <c r="Y2" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z2" s="25" t="s">
         <v>370</v>
-      </c>
-      <c r="X2" s="25">
-        <v>706</v>
-      </c>
-      <c r="Y2" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z2" s="26" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="13.95" customHeight="1">
@@ -2434,7 +2967,7 @@
         <f t="shared" si="0"/>
         <v>44.8</v>
       </c>
-      <c r="N3" s="13">
+      <c r="N3" s="12">
         <v>95</v>
       </c>
       <c r="O3" s="6">
@@ -2444,7 +2977,7 @@
       <c r="P3" s="8">
         <v>288</v>
       </c>
-      <c r="Q3" s="17" t="s">
+      <c r="Q3" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R3" s="1" t="s">
@@ -2455,18 +2988,18 @@
       </c>
       <c r="T3" s="9"/>
       <c r="U3" s="9"/>
-      <c r="V3" s="19"/>
-      <c r="W3" s="20" t="s">
-        <v>373</v>
-      </c>
-      <c r="X3" s="25">
+      <c r="V3" s="18"/>
+      <c r="W3" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="X3" s="24">
         <v>853</v>
       </c>
-      <c r="Y3" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z3" s="26" t="s">
-        <v>374</v>
+      <c r="Y3" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z3" s="25" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="13.95" customHeight="1">
@@ -2508,7 +3041,7 @@
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="N4" s="13">
+      <c r="N4" s="12">
         <v>63.7</v>
       </c>
       <c r="O4" s="6">
@@ -2518,7 +3051,7 @@
       <c r="P4" s="8">
         <v>710</v>
       </c>
-      <c r="Q4" s="17" t="s">
+      <c r="Q4" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R4" s="1" t="s">
@@ -2529,18 +3062,18 @@
       </c>
       <c r="T4" s="9"/>
       <c r="U4" s="9"/>
-      <c r="V4" s="19"/>
-      <c r="W4" s="20" t="s">
-        <v>375</v>
-      </c>
-      <c r="X4" s="25">
+      <c r="V4" s="18"/>
+      <c r="W4" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="X4" s="24">
         <v>1329</v>
       </c>
-      <c r="Y4" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z4" s="26" t="s">
-        <v>376</v>
+      <c r="Y4" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z4" s="25" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="13.95" customHeight="1">
@@ -2582,7 +3115,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="N5" s="13">
+      <c r="N5" s="12">
         <v>40</v>
       </c>
       <c r="O5" s="6">
@@ -2592,7 +3125,7 @@
       <c r="P5" s="8">
         <v>170</v>
       </c>
-      <c r="Q5" s="17" t="s">
+      <c r="Q5" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R5" s="1" t="s">
@@ -2603,18 +3136,18 @@
       </c>
       <c r="T5" s="9"/>
       <c r="U5" s="9"/>
-      <c r="V5" s="19"/>
-      <c r="W5" s="20" t="s">
-        <v>377</v>
-      </c>
-      <c r="X5" s="25">
+      <c r="V5" s="18"/>
+      <c r="W5" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="X5" s="24">
         <v>450</v>
       </c>
-      <c r="Y5" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z5" s="26" t="s">
-        <v>378</v>
+      <c r="Y5" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z5" s="25" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="13.95" customHeight="1">
@@ -2656,7 +3189,7 @@
         <f t="shared" si="0"/>
         <v>33.200000000000003</v>
       </c>
-      <c r="N6" s="14">
+      <c r="N6" s="13">
         <v>58</v>
       </c>
       <c r="O6" s="6">
@@ -2666,7 +3199,7 @@
       <c r="P6" s="8">
         <v>500</v>
       </c>
-      <c r="Q6" s="17" t="s">
+      <c r="Q6" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R6" s="1" t="s">
@@ -2677,18 +3210,18 @@
       </c>
       <c r="T6" s="9"/>
       <c r="U6" s="9"/>
-      <c r="V6" s="19"/>
-      <c r="W6" s="20" t="s">
-        <v>379</v>
-      </c>
-      <c r="X6" s="25">
+      <c r="V6" s="18"/>
+      <c r="W6" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="X6" s="24">
         <v>1140</v>
       </c>
-      <c r="Y6" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z6" s="26" t="s">
-        <v>380</v>
+      <c r="Y6" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z6" s="25" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="13.95" customHeight="1">
@@ -2730,7 +3263,7 @@
         <f t="shared" si="0"/>
         <v>78.180000000000007</v>
       </c>
-      <c r="N7" s="13">
+      <c r="N7" s="12">
         <v>70</v>
       </c>
       <c r="O7" s="6">
@@ -2740,7 +3273,7 @@
       <c r="P7" s="8">
         <v>348.6</v>
       </c>
-      <c r="Q7" s="17" t="s">
+      <c r="Q7" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R7" s="1" t="s">
@@ -2751,18 +3284,18 @@
       </c>
       <c r="T7" s="9"/>
       <c r="U7" s="9"/>
-      <c r="V7" s="19"/>
-      <c r="W7" s="20" t="s">
-        <v>381</v>
-      </c>
-      <c r="X7" s="25">
+      <c r="V7" s="18"/>
+      <c r="W7" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="X7" s="24">
         <v>2</v>
       </c>
-      <c r="Y7" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z7" s="26" t="s">
-        <v>382</v>
+      <c r="Y7" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z7" s="25" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="13.95" customHeight="1">
@@ -2804,7 +3337,7 @@
         <f t="shared" si="0"/>
         <v>48.2</v>
       </c>
-      <c r="N8" s="13">
+      <c r="N8" s="12">
         <v>72</v>
       </c>
       <c r="O8" s="6">
@@ -2814,7 +3347,7 @@
       <c r="P8" s="8">
         <v>306.60000000000002</v>
       </c>
-      <c r="Q8" s="17" t="s">
+      <c r="Q8" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R8" s="1" t="s">
@@ -2825,18 +3358,18 @@
       </c>
       <c r="T8" s="9"/>
       <c r="U8" s="9"/>
-      <c r="V8" s="19"/>
-      <c r="W8" s="20" t="s">
-        <v>383</v>
-      </c>
-      <c r="X8" s="25">
+      <c r="V8" s="18"/>
+      <c r="W8" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="X8" s="24">
         <v>5</v>
       </c>
-      <c r="Y8" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z8" s="26" t="s">
-        <v>384</v>
+      <c r="Y8" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z8" s="25" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="13.95" customHeight="1">
@@ -2878,7 +3411,7 @@
         <f t="shared" si="0"/>
         <v>69.2</v>
       </c>
-      <c r="N9" s="13">
+      <c r="N9" s="12">
         <v>80</v>
       </c>
       <c r="O9" s="6">
@@ -2888,7 +3421,7 @@
       <c r="P9" s="8">
         <v>674.8</v>
       </c>
-      <c r="Q9" s="17" t="s">
+      <c r="Q9" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R9" s="1" t="s">
@@ -2899,18 +3432,18 @@
       </c>
       <c r="T9" s="9"/>
       <c r="U9" s="9"/>
-      <c r="V9" s="19"/>
-      <c r="W9" s="20" t="s">
-        <v>385</v>
-      </c>
-      <c r="X9" s="25">
+      <c r="V9" s="18"/>
+      <c r="W9" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="X9" s="24">
         <v>1130</v>
       </c>
-      <c r="Y9" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z9" s="26" t="s">
-        <v>386</v>
+      <c r="Y9" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z9" s="25" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="13.95" customHeight="1">
@@ -2952,7 +3485,7 @@
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="N10" s="13">
+      <c r="N10" s="12">
         <v>80</v>
       </c>
       <c r="O10" s="6">
@@ -2962,7 +3495,7 @@
       <c r="P10" s="8">
         <v>486</v>
       </c>
-      <c r="Q10" s="17" t="s">
+      <c r="Q10" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R10" s="1" t="s">
@@ -2973,18 +3506,18 @@
       </c>
       <c r="T10" s="9"/>
       <c r="U10" s="9"/>
-      <c r="V10" s="19"/>
-      <c r="W10" s="20" t="s">
-        <v>387</v>
-      </c>
-      <c r="X10" s="25">
+      <c r="V10" s="18"/>
+      <c r="W10" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="X10" s="24">
         <v>1260</v>
       </c>
-      <c r="Y10" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z10" s="26" t="s">
-        <v>388</v>
+      <c r="Y10" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z10" s="25" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="13.95" customHeight="1">
@@ -3026,7 +3559,7 @@
         <f t="shared" si="0"/>
         <v>101.5</v>
       </c>
-      <c r="N11" s="13">
+      <c r="N11" s="12">
         <v>80</v>
       </c>
       <c r="O11" s="6">
@@ -3036,7 +3569,7 @@
       <c r="P11" s="8">
         <v>721.3</v>
       </c>
-      <c r="Q11" s="17" t="s">
+      <c r="Q11" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R11" s="1" t="s">
@@ -3047,18 +3580,18 @@
       </c>
       <c r="T11" s="9"/>
       <c r="U11" s="9"/>
-      <c r="V11" s="19"/>
-      <c r="W11" s="20" t="s">
-        <v>389</v>
-      </c>
-      <c r="X11" s="25">
+      <c r="V11" s="18"/>
+      <c r="W11" s="19" t="s">
+        <v>387</v>
+      </c>
+      <c r="X11" s="24">
         <v>1650</v>
       </c>
-      <c r="Y11" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z11" s="26" t="s">
-        <v>390</v>
+      <c r="Y11" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z11" s="25" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="13.95" customHeight="1">
@@ -3100,7 +3633,7 @@
         <f t="shared" si="0"/>
         <v>2.6000000000000005</v>
       </c>
-      <c r="N12" s="13">
+      <c r="N12" s="12">
         <v>0</v>
       </c>
       <c r="O12" s="6">
@@ -3110,7 +3643,7 @@
       <c r="P12" s="8">
         <v>182.2</v>
       </c>
-      <c r="Q12" s="17" t="s">
+      <c r="Q12" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R12" s="1" t="s">
@@ -3121,18 +3654,18 @@
       </c>
       <c r="T12" s="9"/>
       <c r="U12" s="9"/>
-      <c r="V12" s="19"/>
-      <c r="W12" s="20" t="s">
-        <v>391</v>
-      </c>
-      <c r="X12" s="25">
+      <c r="V12" s="18"/>
+      <c r="W12" s="19" t="s">
+        <v>389</v>
+      </c>
+      <c r="X12" s="24">
         <v>1400</v>
       </c>
-      <c r="Y12" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z12" s="26" t="s">
-        <v>392</v>
+      <c r="Y12" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z12" s="25" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="13.95" customHeight="1">
@@ -3174,7 +3707,7 @@
         <f t="shared" si="0"/>
         <v>8.5</v>
       </c>
-      <c r="N13" s="13">
+      <c r="N13" s="12">
         <v>0</v>
       </c>
       <c r="O13" s="6">
@@ -3184,7 +3717,7 @@
       <c r="P13" s="8">
         <v>137.80000000000001</v>
       </c>
-      <c r="Q13" s="17" t="s">
+      <c r="Q13" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R13" s="1" t="s">
@@ -3195,18 +3728,18 @@
       </c>
       <c r="T13" s="9"/>
       <c r="U13" s="9"/>
-      <c r="V13" s="19"/>
-      <c r="W13" s="20" t="s">
-        <v>393</v>
-      </c>
-      <c r="X13" s="25">
+      <c r="V13" s="18"/>
+      <c r="W13" s="19" t="s">
+        <v>391</v>
+      </c>
+      <c r="X13" s="24">
         <v>1600</v>
       </c>
-      <c r="Y13" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z13" s="26" t="s">
-        <v>394</v>
+      <c r="Y13" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z13" s="25" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="13.95" customHeight="1">
@@ -3248,7 +3781,7 @@
         <f t="shared" si="0"/>
         <v>13.8</v>
       </c>
-      <c r="N14" s="13">
+      <c r="N14" s="12">
         <v>0</v>
       </c>
       <c r="O14" s="6">
@@ -3258,7 +3791,7 @@
       <c r="P14" s="8">
         <v>224.7</v>
       </c>
-      <c r="Q14" s="17" t="s">
+      <c r="Q14" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R14" s="1" t="s">
@@ -3269,18 +3802,18 @@
       </c>
       <c r="T14" s="9"/>
       <c r="U14" s="9"/>
-      <c r="V14" s="19"/>
-      <c r="W14" s="20" t="s">
-        <v>395</v>
-      </c>
-      <c r="X14" s="25">
+      <c r="V14" s="18"/>
+      <c r="W14" s="19" t="s">
+        <v>393</v>
+      </c>
+      <c r="X14" s="24">
         <v>1350</v>
       </c>
-      <c r="Y14" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z14" s="26" t="s">
-        <v>396</v>
+      <c r="Y14" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z14" s="25" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="13.95" customHeight="1">
@@ -3322,7 +3855,7 @@
         <f t="shared" si="0"/>
         <v>1.4000000000000001</v>
       </c>
-      <c r="N15" s="13">
+      <c r="N15" s="12">
         <v>0</v>
       </c>
       <c r="O15" s="6">
@@ -3332,7 +3865,7 @@
       <c r="P15" s="8">
         <v>34.700000000000003</v>
       </c>
-      <c r="Q15" s="17" t="s">
+      <c r="Q15" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R15" s="1" t="s">
@@ -3343,18 +3876,18 @@
       </c>
       <c r="T15" s="9"/>
       <c r="U15" s="9"/>
-      <c r="V15" s="19"/>
-      <c r="W15" s="20" t="s">
-        <v>397</v>
-      </c>
-      <c r="X15" s="25">
+      <c r="V15" s="18"/>
+      <c r="W15" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="X15" s="24">
         <v>900</v>
       </c>
-      <c r="Y15" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z15" s="26" t="s">
-        <v>398</v>
+      <c r="Y15" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z15" s="25" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="13.95" customHeight="1">
@@ -3396,7 +3929,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N16" s="13">
+      <c r="N16" s="12">
         <v>0</v>
       </c>
       <c r="O16" s="6">
@@ -3406,7 +3939,7 @@
       <c r="P16" s="8">
         <v>118.5</v>
       </c>
-      <c r="Q16" s="17" t="s">
+      <c r="Q16" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R16" s="1" t="s">
@@ -3417,18 +3950,18 @@
       </c>
       <c r="T16" s="9"/>
       <c r="U16" s="9"/>
-      <c r="V16" s="19"/>
-      <c r="W16" s="20" t="s">
-        <v>399</v>
-      </c>
-      <c r="X16" s="25">
+      <c r="V16" s="18"/>
+      <c r="W16" s="19" t="s">
+        <v>397</v>
+      </c>
+      <c r="X16" s="24">
         <v>1100</v>
       </c>
-      <c r="Y16" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z16" s="26" t="s">
-        <v>400</v>
+      <c r="Y16" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z16" s="25" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="17" spans="1:26" ht="13.95" customHeight="1">
@@ -3470,7 +4003,7 @@
         <f t="shared" si="0"/>
         <v>17.899999999999999</v>
       </c>
-      <c r="N17" s="13">
+      <c r="N17" s="12">
         <v>86</v>
       </c>
       <c r="O17" s="6">
@@ -3480,7 +4013,7 @@
       <c r="P17" s="8">
         <v>810.2</v>
       </c>
-      <c r="Q17" s="17" t="s">
+      <c r="Q17" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R17" s="1" t="s">
@@ -3491,18 +4024,18 @@
       </c>
       <c r="T17" s="9"/>
       <c r="U17" s="9"/>
-      <c r="V17" s="19"/>
-      <c r="W17" s="20" t="s">
-        <v>401</v>
-      </c>
-      <c r="X17" s="25">
+      <c r="V17" s="18"/>
+      <c r="W17" s="19" t="s">
+        <v>399</v>
+      </c>
+      <c r="X17" s="24">
         <v>1300</v>
       </c>
-      <c r="Y17" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z17" s="26" t="s">
-        <v>402</v>
+      <c r="Y17" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z17" s="25" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="18" spans="1:26" ht="13.95" customHeight="1">
@@ -3544,7 +4077,7 @@
         <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
-      <c r="N18" s="13">
+      <c r="N18" s="12">
         <v>65</v>
       </c>
       <c r="O18" s="6">
@@ -3554,7 +4087,7 @@
       <c r="P18" s="8">
         <v>339.2</v>
       </c>
-      <c r="Q18" s="17" t="s">
+      <c r="Q18" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R18" s="1" t="s">
@@ -3565,18 +4098,18 @@
       </c>
       <c r="T18" s="9"/>
       <c r="U18" s="9"/>
-      <c r="V18" s="19"/>
-      <c r="W18" s="20" t="s">
-        <v>403</v>
-      </c>
-      <c r="X18" s="25">
+      <c r="V18" s="18"/>
+      <c r="W18" s="19" t="s">
+        <v>401</v>
+      </c>
+      <c r="X18" s="24">
         <v>900</v>
       </c>
-      <c r="Y18" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z18" s="26" t="s">
-        <v>404</v>
+      <c r="Y18" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z18" s="25" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="19" spans="1:26" ht="13.95" customHeight="1">
@@ -3618,7 +4151,7 @@
         <f t="shared" si="0"/>
         <v>9.8600000000000012</v>
       </c>
-      <c r="N19" s="13">
+      <c r="N19" s="12">
         <v>0</v>
       </c>
       <c r="O19" s="6">
@@ -3628,7 +4161,7 @@
       <c r="P19" s="8">
         <v>302</v>
       </c>
-      <c r="Q19" s="17" t="s">
+      <c r="Q19" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R19" s="1" t="s">
@@ -3639,18 +4172,18 @@
       </c>
       <c r="T19" s="9"/>
       <c r="U19" s="9"/>
-      <c r="V19" s="19"/>
-      <c r="W19" s="20" t="s">
-        <v>405</v>
-      </c>
-      <c r="X19" s="25">
+      <c r="V19" s="18"/>
+      <c r="W19" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="X19" s="24">
         <v>1200</v>
       </c>
-      <c r="Y19" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z19" s="26" t="s">
-        <v>406</v>
+      <c r="Y19" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z19" s="25" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="20" spans="1:26" ht="13.95" customHeight="1">
@@ -3692,7 +4225,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N20" s="13">
+      <c r="N20" s="12">
         <v>0</v>
       </c>
       <c r="O20" s="6">
@@ -3702,7 +4235,7 @@
       <c r="P20" s="8">
         <v>700</v>
       </c>
-      <c r="Q20" s="17" t="s">
+      <c r="Q20" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R20" s="1" t="s">
@@ -3713,18 +4246,18 @@
       </c>
       <c r="T20" s="9"/>
       <c r="U20" s="9"/>
-      <c r="V20" s="19"/>
-      <c r="W20" s="20" t="s">
-        <v>407</v>
-      </c>
-      <c r="X20" s="25">
+      <c r="V20" s="18"/>
+      <c r="W20" s="19" t="s">
+        <v>405</v>
+      </c>
+      <c r="X20" s="24">
         <v>80</v>
       </c>
-      <c r="Y20" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z20" s="26" t="s">
-        <v>408</v>
+      <c r="Y20" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z20" s="25" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="21" spans="1:26" ht="13.95" customHeight="1">
@@ -3766,7 +4299,7 @@
         <f t="shared" si="0"/>
         <v>2.69</v>
       </c>
-      <c r="N21" s="13">
+      <c r="N21" s="12">
         <v>0</v>
       </c>
       <c r="O21" s="6">
@@ -3776,7 +4309,7 @@
       <c r="P21" s="8">
         <v>142</v>
       </c>
-      <c r="Q21" s="17" t="s">
+      <c r="Q21" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R21" s="1" t="s">
@@ -3787,18 +4320,18 @@
       </c>
       <c r="T21" s="9"/>
       <c r="U21" s="9"/>
-      <c r="V21" s="19"/>
-      <c r="W21" s="20" t="s">
-        <v>409</v>
-      </c>
-      <c r="X21" s="25">
+      <c r="V21" s="18"/>
+      <c r="W21" s="19" t="s">
+        <v>407</v>
+      </c>
+      <c r="X21" s="24">
         <v>540</v>
       </c>
-      <c r="Y21" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z21" s="26" t="s">
-        <v>410</v>
+      <c r="Y21" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z21" s="25" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="22" spans="1:26" ht="13.95" customHeight="1">
@@ -3840,7 +4373,7 @@
         <f t="shared" si="0"/>
         <v>69.58</v>
       </c>
-      <c r="N22" s="13">
+      <c r="N22" s="12">
         <v>49.3</v>
       </c>
       <c r="O22" s="6">
@@ -3850,7 +4383,7 @@
       <c r="P22" s="8">
         <v>451</v>
       </c>
-      <c r="Q22" s="17" t="s">
+      <c r="Q22" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R22" s="1" t="s">
@@ -3861,18 +4394,18 @@
       </c>
       <c r="T22" s="9"/>
       <c r="U22" s="9"/>
-      <c r="V22" s="19"/>
-      <c r="W22" s="20" t="s">
-        <v>411</v>
-      </c>
-      <c r="X22" s="25">
+      <c r="V22" s="18"/>
+      <c r="W22" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="X22" s="24">
         <v>1800</v>
       </c>
-      <c r="Y22" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z22" s="26" t="s">
-        <v>412</v>
+      <c r="Y22" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z22" s="25" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="23" spans="1:26" ht="13.95" customHeight="1">
@@ -3914,7 +4447,7 @@
         <f t="shared" si="0"/>
         <v>36.25</v>
       </c>
-      <c r="N23" s="13">
+      <c r="N23" s="12">
         <v>81.599999999999994</v>
       </c>
       <c r="O23" s="6">
@@ -3924,7 +4457,7 @@
       <c r="P23" s="8">
         <v>220</v>
       </c>
-      <c r="Q23" s="17" t="s">
+      <c r="Q23" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R23" s="1" t="s">
@@ -3935,18 +4468,18 @@
       </c>
       <c r="T23" s="9"/>
       <c r="U23" s="9"/>
-      <c r="V23" s="19"/>
-      <c r="W23" s="20" t="s">
-        <v>413</v>
-      </c>
-      <c r="X23" s="25">
+      <c r="V23" s="18"/>
+      <c r="W23" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="X23" s="24">
         <v>1500</v>
       </c>
-      <c r="Y23" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z23" s="26" t="s">
-        <v>414</v>
+      <c r="Y23" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z23" s="25" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="24" spans="1:26" ht="13.95" customHeight="1">
@@ -3988,7 +4521,7 @@
         <f t="shared" si="0"/>
         <v>79.800000000000011</v>
       </c>
-      <c r="N24" s="13">
+      <c r="N24" s="12">
         <v>62</v>
       </c>
       <c r="O24" s="6">
@@ -3998,7 +4531,7 @@
       <c r="P24" s="8">
         <v>462</v>
       </c>
-      <c r="Q24" s="17" t="s">
+      <c r="Q24" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R24" s="1" t="s">
@@ -4009,18 +4542,18 @@
       </c>
       <c r="T24" s="9"/>
       <c r="U24" s="9"/>
-      <c r="V24" s="19"/>
-      <c r="W24" s="20" t="s">
-        <v>415</v>
-      </c>
-      <c r="X24" s="25">
+      <c r="V24" s="18"/>
+      <c r="W24" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="X24" s="24">
         <v>2100</v>
       </c>
-      <c r="Y24" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z24" s="26" t="s">
-        <v>416</v>
+      <c r="Y24" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z24" s="25" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="25" spans="1:26" ht="13.95" customHeight="1">
@@ -4062,7 +4595,7 @@
         <f t="shared" si="0"/>
         <v>55.050000000000004</v>
       </c>
-      <c r="N25" s="13">
+      <c r="N25" s="12">
         <v>59</v>
       </c>
       <c r="O25" s="6">
@@ -4072,7 +4605,7 @@
       <c r="P25" s="8">
         <v>302.5</v>
       </c>
-      <c r="Q25" s="17" t="s">
+      <c r="Q25" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R25" s="1" t="s">
@@ -4083,18 +4616,18 @@
       </c>
       <c r="T25" s="9"/>
       <c r="U25" s="9"/>
-      <c r="V25" s="19"/>
-      <c r="W25" s="20" t="s">
-        <v>417</v>
-      </c>
-      <c r="X25" s="25">
+      <c r="V25" s="18"/>
+      <c r="W25" s="19" t="s">
+        <v>415</v>
+      </c>
+      <c r="X25" s="24">
         <v>1700</v>
       </c>
-      <c r="Y25" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z25" s="26" t="s">
-        <v>418</v>
+      <c r="Y25" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z25" s="25" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="26" spans="1:26" ht="13.95" customHeight="1">
@@ -4136,7 +4669,7 @@
         <f t="shared" si="0"/>
         <v>84.300000000000011</v>
       </c>
-      <c r="N26" s="13">
+      <c r="N26" s="12">
         <v>50</v>
       </c>
       <c r="O26" s="6">
@@ -4146,7 +4679,7 @@
       <c r="P26" s="8">
         <v>572</v>
       </c>
-      <c r="Q26" s="17" t="s">
+      <c r="Q26" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R26" s="1" t="s">
@@ -4157,18 +4690,18 @@
       </c>
       <c r="T26" s="9"/>
       <c r="U26" s="9"/>
-      <c r="V26" s="19"/>
-      <c r="W26" s="20" t="s">
-        <v>419</v>
-      </c>
-      <c r="X26" s="25">
+      <c r="V26" s="18"/>
+      <c r="W26" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="X26" s="24">
         <v>2400</v>
       </c>
-      <c r="Y26" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z26" s="26" t="s">
-        <v>420</v>
+      <c r="Y26" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z26" s="25" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="27" spans="1:26" ht="13.95" customHeight="1">
@@ -4210,7 +4743,7 @@
         <f t="shared" si="0"/>
         <v>28.500000000000004</v>
       </c>
-      <c r="N27" s="13">
+      <c r="N27" s="12">
         <v>73.400000000000006</v>
       </c>
       <c r="O27" s="6">
@@ -4220,7 +4753,7 @@
       <c r="P27" s="8">
         <v>185</v>
       </c>
-      <c r="Q27" s="17" t="s">
+      <c r="Q27" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R27" s="1" t="s">
@@ -4231,18 +4764,18 @@
       </c>
       <c r="T27" s="9"/>
       <c r="U27" s="9"/>
-      <c r="V27" s="19"/>
-      <c r="W27" s="20" t="s">
+      <c r="V27" s="18"/>
+      <c r="W27" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="X27" s="24">
+        <v>15</v>
+      </c>
+      <c r="Y27" s="25" t="s">
+        <v>420</v>
+      </c>
+      <c r="Z27" s="25" t="s">
         <v>421</v>
-      </c>
-      <c r="X27" s="25">
-        <v>15</v>
-      </c>
-      <c r="Y27" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="Z27" s="26" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="28" spans="1:26" ht="13.95" customHeight="1">
@@ -4284,7 +4817,7 @@
         <f t="shared" si="0"/>
         <v>38.97</v>
       </c>
-      <c r="N28" s="13">
+      <c r="N28" s="12">
         <v>82</v>
       </c>
       <c r="O28" s="6">
@@ -4294,7 +4827,7 @@
       <c r="P28" s="8">
         <v>700</v>
       </c>
-      <c r="Q28" s="17" t="s">
+      <c r="Q28" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R28" s="1" t="s">
@@ -4305,18 +4838,18 @@
       </c>
       <c r="T28" s="9"/>
       <c r="U28" s="9"/>
-      <c r="V28" s="19"/>
-      <c r="W28" s="20" t="s">
-        <v>424</v>
-      </c>
-      <c r="X28" s="25">
+      <c r="V28" s="18"/>
+      <c r="W28" s="19" t="s">
+        <v>422</v>
+      </c>
+      <c r="X28" s="24">
         <v>800</v>
       </c>
-      <c r="Y28" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z28" s="26" t="s">
-        <v>425</v>
+      <c r="Y28" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z28" s="25" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="29" spans="1:26" ht="13.95" customHeight="1">
@@ -4358,7 +4891,7 @@
         <f t="shared" si="0"/>
         <v>33.78</v>
       </c>
-      <c r="N29" s="13">
+      <c r="N29" s="12">
         <v>71</v>
       </c>
       <c r="O29" s="6">
@@ -4368,7 +4901,7 @@
       <c r="P29" s="8">
         <v>370</v>
       </c>
-      <c r="Q29" s="17" t="s">
+      <c r="Q29" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R29" s="1" t="s">
@@ -4379,18 +4912,18 @@
       </c>
       <c r="T29" s="9"/>
       <c r="U29" s="9"/>
-      <c r="V29" s="19"/>
-      <c r="W29" s="20" t="s">
-        <v>426</v>
-      </c>
-      <c r="X29" s="25">
+      <c r="V29" s="18"/>
+      <c r="W29" s="19" t="s">
+        <v>424</v>
+      </c>
+      <c r="X29" s="24">
         <v>1000</v>
       </c>
-      <c r="Y29" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z29" s="26" t="s">
-        <v>427</v>
+      <c r="Y29" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z29" s="25" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="30" spans="1:26" ht="13.95" customHeight="1">
@@ -4432,7 +4965,7 @@
         <f t="shared" si="0"/>
         <v>37.93</v>
       </c>
-      <c r="N30" s="14">
+      <c r="N30" s="13">
         <v>65</v>
       </c>
       <c r="O30" s="6">
@@ -4442,7 +4975,7 @@
       <c r="P30" s="8">
         <v>211.2</v>
       </c>
-      <c r="Q30" s="17" t="s">
+      <c r="Q30" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R30" s="1" t="s">
@@ -4453,18 +4986,18 @@
       </c>
       <c r="T30" s="9"/>
       <c r="U30" s="9"/>
-      <c r="V30" s="19"/>
-      <c r="W30" s="20" t="s">
-        <v>428</v>
-      </c>
-      <c r="X30" s="25">
+      <c r="V30" s="18"/>
+      <c r="W30" s="19" t="s">
+        <v>426</v>
+      </c>
+      <c r="X30" s="24">
         <v>400</v>
       </c>
-      <c r="Y30" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z30" s="26" t="s">
-        <v>429</v>
+      <c r="Y30" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z30" s="25" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="31" spans="1:26" ht="13.95" customHeight="1">
@@ -4506,7 +5039,7 @@
         <f t="shared" si="0"/>
         <v>60.3</v>
       </c>
-      <c r="N31" s="15">
+      <c r="N31" s="14">
         <v>56.5</v>
       </c>
       <c r="O31" s="6">
@@ -4516,7 +5049,7 @@
       <c r="P31" s="8">
         <v>355</v>
       </c>
-      <c r="Q31" s="17" t="s">
+      <c r="Q31" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R31" s="1" t="s">
@@ -4527,18 +5060,18 @@
       </c>
       <c r="T31" s="9"/>
       <c r="U31" s="9"/>
-      <c r="V31" s="19"/>
-      <c r="W31" s="20" t="s">
-        <v>430</v>
-      </c>
-      <c r="X31" s="25">
+      <c r="V31" s="18"/>
+      <c r="W31" s="19" t="s">
+        <v>428</v>
+      </c>
+      <c r="X31" s="24">
         <v>2100</v>
       </c>
-      <c r="Y31" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z31" s="26" t="s">
-        <v>431</v>
+      <c r="Y31" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z31" s="25" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="32" spans="1:26" ht="13.95" customHeight="1">
@@ -4580,7 +5113,7 @@
         <f t="shared" si="0"/>
         <v>39.1</v>
       </c>
-      <c r="N32" s="15">
+      <c r="N32" s="14">
         <v>55.3</v>
       </c>
       <c r="O32" s="6">
@@ -4590,7 +5123,7 @@
       <c r="P32" s="8">
         <v>324</v>
       </c>
-      <c r="Q32" s="17" t="s">
+      <c r="Q32" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R32" s="1" t="s">
@@ -4601,18 +5134,18 @@
       </c>
       <c r="T32" s="9"/>
       <c r="U32" s="9"/>
-      <c r="V32" s="19"/>
-      <c r="W32" s="20" t="s">
-        <v>432</v>
-      </c>
-      <c r="X32" s="25">
+      <c r="V32" s="18"/>
+      <c r="W32" s="19" t="s">
+        <v>430</v>
+      </c>
+      <c r="X32" s="24">
         <v>600</v>
       </c>
-      <c r="Y32" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z32" s="26" t="s">
-        <v>433</v>
+      <c r="Y32" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z32" s="25" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="33" spans="1:26" ht="13.95" customHeight="1">
@@ -4654,7 +5187,7 @@
         <f t="shared" si="0"/>
         <v>24.419999999999998</v>
       </c>
-      <c r="N33" s="16">
+      <c r="N33" s="15">
         <v>73</v>
       </c>
       <c r="O33" s="6">
@@ -4664,7 +5197,7 @@
       <c r="P33" s="8">
         <v>161.5</v>
       </c>
-      <c r="Q33" s="17" t="s">
+      <c r="Q33" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R33" s="1" t="s">
@@ -4675,18 +5208,18 @@
       </c>
       <c r="T33" s="9"/>
       <c r="U33" s="9"/>
-      <c r="V33" s="19"/>
-      <c r="W33" s="20" t="s">
-        <v>434</v>
-      </c>
-      <c r="X33" s="25">
+      <c r="V33" s="18"/>
+      <c r="W33" s="19" t="s">
+        <v>432</v>
+      </c>
+      <c r="X33" s="24">
         <v>350</v>
       </c>
-      <c r="Y33" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z33" s="26" t="s">
-        <v>435</v>
+      <c r="Y33" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z33" s="25" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="34" spans="1:26" ht="13.95" customHeight="1">
@@ -4728,7 +5261,7 @@
         <f t="shared" ref="M34:M59" si="2">IF(OR(I34="",J34=""),"",MAX(I34-J34,0))</f>
         <v>112.95</v>
       </c>
-      <c r="N34" s="16">
+      <c r="N34" s="15">
         <v>80</v>
       </c>
       <c r="O34" s="6">
@@ -4738,7 +5271,7 @@
       <c r="P34" s="8">
         <v>640.5</v>
       </c>
-      <c r="Q34" s="17" t="s">
+      <c r="Q34" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R34" s="1" t="s">
@@ -4749,18 +5282,18 @@
       </c>
       <c r="T34" s="9"/>
       <c r="U34" s="9"/>
-      <c r="V34" s="19"/>
-      <c r="W34" s="20" t="s">
-        <v>436</v>
-      </c>
-      <c r="X34" s="25">
+      <c r="V34" s="18"/>
+      <c r="W34" s="19" t="s">
+        <v>434</v>
+      </c>
+      <c r="X34" s="24">
         <v>1100</v>
       </c>
-      <c r="Y34" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z34" s="26" t="s">
-        <v>437</v>
+      <c r="Y34" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z34" s="25" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="35" spans="1:26" ht="13.95" customHeight="1">
@@ -4802,7 +5335,7 @@
         <f t="shared" si="2"/>
         <v>33.22</v>
       </c>
-      <c r="N35" s="16">
+      <c r="N35" s="15">
         <v>28</v>
       </c>
       <c r="O35" s="6">
@@ -4812,7 +5345,7 @@
       <c r="P35" s="8">
         <v>349.8</v>
       </c>
-      <c r="Q35" s="17" t="s">
+      <c r="Q35" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R35" s="1" t="s">
@@ -4823,18 +5356,18 @@
       </c>
       <c r="T35" s="9"/>
       <c r="U35" s="9"/>
-      <c r="V35" s="19"/>
-      <c r="W35" s="20" t="s">
-        <v>438</v>
-      </c>
-      <c r="X35" s="25">
+      <c r="V35" s="18"/>
+      <c r="W35" s="19" t="s">
+        <v>436</v>
+      </c>
+      <c r="X35" s="24">
         <v>900</v>
       </c>
-      <c r="Y35" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z35" s="26" t="s">
-        <v>439</v>
+      <c r="Y35" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z35" s="25" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="36" spans="1:26" ht="13.95" customHeight="1">
@@ -4876,7 +5409,7 @@
         <f t="shared" si="2"/>
         <v>6.58</v>
       </c>
-      <c r="N36" s="16">
+      <c r="N36" s="15">
         <v>39</v>
       </c>
       <c r="O36" s="6">
@@ -4886,7 +5419,7 @@
       <c r="P36" s="8">
         <v>41</v>
       </c>
-      <c r="Q36" s="17" t="s">
+      <c r="Q36" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R36" s="1" t="s">
@@ -4897,18 +5430,18 @@
       </c>
       <c r="T36" s="9"/>
       <c r="U36" s="9"/>
-      <c r="V36" s="19"/>
-      <c r="W36" s="20" t="s">
-        <v>440</v>
-      </c>
-      <c r="X36" s="25">
+      <c r="V36" s="18"/>
+      <c r="W36" s="19" t="s">
+        <v>438</v>
+      </c>
+      <c r="X36" s="24">
         <v>69</v>
       </c>
-      <c r="Y36" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="Z36" s="26" t="s">
-        <v>441</v>
+      <c r="Y36" s="25" t="s">
+        <v>420</v>
+      </c>
+      <c r="Z36" s="25" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="37" spans="1:26" ht="13.95" customHeight="1">
@@ -4950,7 +5483,7 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="N37" s="16">
+      <c r="N37" s="15">
         <v>31</v>
       </c>
       <c r="O37" s="6">
@@ -4960,7 +5493,7 @@
       <c r="P37" s="8">
         <v>70.3</v>
       </c>
-      <c r="Q37" s="17" t="s">
+      <c r="Q37" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R37" s="1" t="s">
@@ -4971,18 +5504,18 @@
       </c>
       <c r="T37" s="9"/>
       <c r="U37" s="9"/>
-      <c r="V37" s="19"/>
-      <c r="W37" s="20" t="s">
-        <v>442</v>
-      </c>
-      <c r="X37" s="25">
+      <c r="V37" s="18"/>
+      <c r="W37" s="19" t="s">
+        <v>440</v>
+      </c>
+      <c r="X37" s="24">
         <v>270</v>
       </c>
-      <c r="Y37" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z37" s="26" t="s">
-        <v>443</v>
+      <c r="Y37" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z37" s="25" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="38" spans="1:26" ht="13.95" customHeight="1">
@@ -5024,7 +5557,7 @@
         <f t="shared" si="2"/>
         <v>11.14</v>
       </c>
-      <c r="N38" s="16">
+      <c r="N38" s="15">
         <v>38</v>
       </c>
       <c r="O38" s="6">
@@ -5034,7 +5567,7 @@
       <c r="P38" s="8">
         <v>45</v>
       </c>
-      <c r="Q38" s="17" t="s">
+      <c r="Q38" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R38" s="1" t="s">
@@ -5045,18 +5578,18 @@
       </c>
       <c r="T38" s="9"/>
       <c r="U38" s="9"/>
-      <c r="V38" s="19"/>
-      <c r="W38" s="20" t="s">
-        <v>444</v>
-      </c>
-      <c r="X38" s="25">
+      <c r="V38" s="18"/>
+      <c r="W38" s="19" t="s">
+        <v>442</v>
+      </c>
+      <c r="X38" s="24">
         <v>1</v>
       </c>
-      <c r="Y38" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="Z38" s="26" t="s">
-        <v>445</v>
+      <c r="Y38" s="25" t="s">
+        <v>420</v>
+      </c>
+      <c r="Z38" s="25" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="39" spans="1:26" ht="13.95" customHeight="1">
@@ -5098,7 +5631,7 @@
         <f t="shared" si="2"/>
         <v>8.44</v>
       </c>
-      <c r="N39" s="15">
+      <c r="N39" s="14">
         <v>47</v>
       </c>
       <c r="O39" s="6">
@@ -5108,7 +5641,7 @@
       <c r="P39" s="8">
         <v>39</v>
       </c>
-      <c r="Q39" s="17" t="s">
+      <c r="Q39" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R39" s="1" t="s">
@@ -5119,18 +5652,18 @@
       </c>
       <c r="T39" s="9"/>
       <c r="U39" s="9"/>
-      <c r="V39" s="19"/>
-      <c r="W39" s="20" t="s">
-        <v>446</v>
-      </c>
-      <c r="X39" s="25">
+      <c r="V39" s="18"/>
+      <c r="W39" s="19" t="s">
+        <v>444</v>
+      </c>
+      <c r="X39" s="24">
         <v>2</v>
       </c>
-      <c r="Y39" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="Z39" s="26" t="s">
-        <v>447</v>
+      <c r="Y39" s="25" t="s">
+        <v>420</v>
+      </c>
+      <c r="Z39" s="25" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="40" spans="1:26" ht="13.95" customHeight="1">
@@ -5172,7 +5705,7 @@
         <f t="shared" si="2"/>
         <v>15.26</v>
       </c>
-      <c r="N40" s="15">
+      <c r="N40" s="14">
         <v>80</v>
       </c>
       <c r="O40" s="6">
@@ -5182,7 +5715,7 @@
       <c r="P40" s="8">
         <v>62</v>
       </c>
-      <c r="Q40" s="17" t="s">
+      <c r="Q40" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R40" s="1" t="s">
@@ -5193,18 +5726,18 @@
       </c>
       <c r="T40" s="9"/>
       <c r="U40" s="9"/>
-      <c r="V40" s="19"/>
-      <c r="W40" s="20" t="s">
-        <v>448</v>
-      </c>
-      <c r="X40" s="25">
+      <c r="V40" s="18"/>
+      <c r="W40" s="19" t="s">
+        <v>446</v>
+      </c>
+      <c r="X40" s="24">
         <v>2</v>
       </c>
-      <c r="Y40" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="Z40" s="26" t="s">
-        <v>449</v>
+      <c r="Y40" s="25" t="s">
+        <v>420</v>
+      </c>
+      <c r="Z40" s="25" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="41" spans="1:26" ht="13.95" customHeight="1">
@@ -5246,7 +5779,7 @@
         <f t="shared" si="2"/>
         <v>11.18</v>
       </c>
-      <c r="N41" s="15">
+      <c r="N41" s="14">
         <v>34</v>
       </c>
       <c r="O41" s="6">
@@ -5256,7 +5789,7 @@
       <c r="P41" s="8">
         <v>49</v>
       </c>
-      <c r="Q41" s="17" t="s">
+      <c r="Q41" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R41" s="1" t="s">
@@ -5267,18 +5800,18 @@
       </c>
       <c r="T41" s="9"/>
       <c r="U41" s="9"/>
-      <c r="V41" s="19"/>
-      <c r="W41" s="20" t="s">
-        <v>450</v>
-      </c>
-      <c r="X41" s="25">
+      <c r="V41" s="18"/>
+      <c r="W41" s="19" t="s">
+        <v>448</v>
+      </c>
+      <c r="X41" s="24">
         <v>0</v>
       </c>
-      <c r="Y41" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="Z41" s="26" t="s">
-        <v>451</v>
+      <c r="Y41" s="25" t="s">
+        <v>420</v>
+      </c>
+      <c r="Z41" s="25" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="42" spans="1:26" ht="13.95" customHeight="1">
@@ -5320,7 +5853,7 @@
         <f t="shared" si="2"/>
         <v>33.6</v>
       </c>
-      <c r="N42" s="15">
+      <c r="N42" s="14">
         <v>46</v>
       </c>
       <c r="O42" s="6">
@@ -5330,7 +5863,7 @@
       <c r="P42" s="8">
         <v>259</v>
       </c>
-      <c r="Q42" s="17" t="s">
+      <c r="Q42" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R42" s="1" t="s">
@@ -5341,18 +5874,18 @@
       </c>
       <c r="T42" s="9"/>
       <c r="U42" s="9"/>
-      <c r="V42" s="19"/>
-      <c r="W42" s="20" t="s">
-        <v>452</v>
-      </c>
-      <c r="X42" s="25">
+      <c r="V42" s="18"/>
+      <c r="W42" s="19" t="s">
+        <v>450</v>
+      </c>
+      <c r="X42" s="24">
         <v>210</v>
       </c>
-      <c r="Y42" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z42" s="26" t="s">
-        <v>453</v>
+      <c r="Y42" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z42" s="25" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="43" spans="1:26" ht="13.95" customHeight="1">
@@ -5394,7 +5927,7 @@
         <f t="shared" si="2"/>
         <v>40.25</v>
       </c>
-      <c r="N43" s="15">
+      <c r="N43" s="14">
         <v>73</v>
       </c>
       <c r="O43" s="6">
@@ -5404,7 +5937,7 @@
       <c r="P43" s="8">
         <v>270</v>
       </c>
-      <c r="Q43" s="17" t="s">
+      <c r="Q43" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R43" s="1" t="s">
@@ -5415,18 +5948,18 @@
       </c>
       <c r="T43" s="9"/>
       <c r="U43" s="9"/>
-      <c r="V43" s="19"/>
-      <c r="W43" s="20" t="s">
-        <v>454</v>
-      </c>
-      <c r="X43" s="25">
+      <c r="V43" s="18"/>
+      <c r="W43" s="19" t="s">
+        <v>452</v>
+      </c>
+      <c r="X43" s="24">
         <v>330</v>
       </c>
-      <c r="Y43" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z43" s="26" t="s">
-        <v>455</v>
+      <c r="Y43" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z43" s="25" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="44" spans="1:26" ht="13.95" customHeight="1">
@@ -5468,7 +6001,7 @@
         <f t="shared" si="2"/>
         <v>39.57</v>
       </c>
-      <c r="N44" s="15">
+      <c r="N44" s="14">
         <v>68</v>
       </c>
       <c r="O44" s="6">
@@ -5478,7 +6011,7 @@
       <c r="P44" s="8">
         <v>192</v>
       </c>
-      <c r="Q44" s="17" t="s">
+      <c r="Q44" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R44" s="1" t="s">
@@ -5489,18 +6022,18 @@
       </c>
       <c r="T44" s="9"/>
       <c r="U44" s="9"/>
-      <c r="V44" s="19"/>
-      <c r="W44" s="20" t="s">
-        <v>456</v>
-      </c>
-      <c r="X44" s="25">
+      <c r="V44" s="18"/>
+      <c r="W44" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="X44" s="24">
         <v>300</v>
       </c>
-      <c r="Y44" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z44" s="26" t="s">
-        <v>457</v>
+      <c r="Y44" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z44" s="25" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="45" spans="1:26" ht="13.95" customHeight="1">
@@ -5550,7 +6083,7 @@
       <c r="P45" s="8">
         <v>150</v>
       </c>
-      <c r="Q45" s="17" t="s">
+      <c r="Q45" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R45" s="1" t="s">
@@ -5561,18 +6094,18 @@
       </c>
       <c r="T45" s="9"/>
       <c r="U45" s="9"/>
-      <c r="V45" s="19"/>
-      <c r="W45" s="20" t="s">
-        <v>458</v>
-      </c>
-      <c r="X45" s="25">
+      <c r="V45" s="18"/>
+      <c r="W45" s="19" t="s">
+        <v>456</v>
+      </c>
+      <c r="X45" s="24">
         <v>124</v>
       </c>
-      <c r="Y45" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="Z45" s="26" t="s">
-        <v>459</v>
+      <c r="Y45" s="25" t="s">
+        <v>420</v>
+      </c>
+      <c r="Z45" s="25" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="46" spans="1:26" ht="13.95" customHeight="1">
@@ -5622,7 +6155,7 @@
       <c r="P46" s="8">
         <v>135</v>
       </c>
-      <c r="Q46" s="17" t="s">
+      <c r="Q46" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R46" s="1" t="s">
@@ -5633,18 +6166,18 @@
       </c>
       <c r="T46" s="9"/>
       <c r="U46" s="9"/>
-      <c r="V46" s="19"/>
-      <c r="W46" s="20" t="s">
-        <v>460</v>
-      </c>
-      <c r="X46" s="25">
+      <c r="V46" s="18"/>
+      <c r="W46" s="19" t="s">
+        <v>458</v>
+      </c>
+      <c r="X46" s="24">
         <v>10</v>
       </c>
-      <c r="Y46" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z46" s="26" t="s">
-        <v>461</v>
+      <c r="Y46" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z46" s="25" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="47" spans="1:26" ht="13.95" customHeight="1">
@@ -5694,7 +6227,7 @@
       <c r="P47" s="8">
         <v>120</v>
       </c>
-      <c r="Q47" s="17" t="s">
+      <c r="Q47" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R47" s="1" t="s">
@@ -5705,18 +6238,18 @@
       </c>
       <c r="T47" s="9"/>
       <c r="U47" s="9"/>
-      <c r="V47" s="19"/>
-      <c r="W47" s="20" t="s">
-        <v>462</v>
-      </c>
-      <c r="X47" s="25">
+      <c r="V47" s="18"/>
+      <c r="W47" s="19" t="s">
+        <v>460</v>
+      </c>
+      <c r="X47" s="24">
         <v>70</v>
       </c>
-      <c r="Y47" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="Z47" s="26" t="s">
-        <v>463</v>
+      <c r="Y47" s="25" t="s">
+        <v>420</v>
+      </c>
+      <c r="Z47" s="25" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="48" spans="1:26" ht="13.95" customHeight="1">
@@ -5766,7 +6299,7 @@
       <c r="P48" s="8">
         <v>20</v>
       </c>
-      <c r="Q48" s="17" t="s">
+      <c r="Q48" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R48" s="1" t="s">
@@ -5777,18 +6310,18 @@
       </c>
       <c r="T48" s="9"/>
       <c r="U48" s="9"/>
-      <c r="V48" s="19"/>
-      <c r="W48" s="20" t="s">
-        <v>464</v>
-      </c>
-      <c r="X48" s="25">
+      <c r="V48" s="18"/>
+      <c r="W48" s="19" t="s">
+        <v>462</v>
+      </c>
+      <c r="X48" s="24">
         <v>5</v>
       </c>
-      <c r="Y48" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="Z48" s="26" t="s">
-        <v>465</v>
+      <c r="Y48" s="25" t="s">
+        <v>420</v>
+      </c>
+      <c r="Z48" s="25" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="49" spans="1:26" ht="13.95" customHeight="1">
@@ -5838,7 +6371,7 @@
       <c r="P49" s="8">
         <v>15</v>
       </c>
-      <c r="Q49" s="17" t="s">
+      <c r="Q49" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R49" s="1" t="s">
@@ -5849,18 +6382,18 @@
       </c>
       <c r="T49" s="9"/>
       <c r="U49" s="9"/>
-      <c r="V49" s="19"/>
-      <c r="W49" s="20" t="s">
-        <v>466</v>
-      </c>
-      <c r="X49" s="25">
+      <c r="V49" s="18"/>
+      <c r="W49" s="19" t="s">
+        <v>464</v>
+      </c>
+      <c r="X49" s="24">
         <v>220</v>
       </c>
-      <c r="Y49" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z49" s="26" t="s">
-        <v>467</v>
+      <c r="Y49" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z49" s="25" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="50" spans="1:26" ht="13.95" customHeight="1">
@@ -5910,7 +6443,7 @@
       <c r="P50" s="8">
         <v>25</v>
       </c>
-      <c r="Q50" s="17" t="s">
+      <c r="Q50" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R50" s="1" t="s">
@@ -5921,18 +6454,18 @@
       </c>
       <c r="T50" s="9"/>
       <c r="U50" s="9"/>
-      <c r="V50" s="19"/>
-      <c r="W50" s="20" t="s">
-        <v>468</v>
-      </c>
-      <c r="X50" s="25">
+      <c r="V50" s="18"/>
+      <c r="W50" s="19" t="s">
+        <v>466</v>
+      </c>
+      <c r="X50" s="24">
         <v>4</v>
       </c>
-      <c r="Y50" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="Z50" s="26" t="s">
-        <v>469</v>
+      <c r="Y50" s="25" t="s">
+        <v>420</v>
+      </c>
+      <c r="Z50" s="25" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="51" spans="1:26" ht="13.95" customHeight="1">
@@ -5982,7 +6515,7 @@
       <c r="P51" s="8">
         <v>25</v>
       </c>
-      <c r="Q51" s="17" t="s">
+      <c r="Q51" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R51" s="1" t="s">
@@ -5993,18 +6526,18 @@
       </c>
       <c r="T51" s="9"/>
       <c r="U51" s="9"/>
-      <c r="V51" s="19"/>
-      <c r="W51" s="20" t="s">
-        <v>470</v>
-      </c>
-      <c r="X51" s="25">
+      <c r="V51" s="18"/>
+      <c r="W51" s="19" t="s">
+        <v>468</v>
+      </c>
+      <c r="X51" s="24">
         <v>18</v>
       </c>
-      <c r="Y51" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="Z51" s="26" t="s">
-        <v>471</v>
+      <c r="Y51" s="25" t="s">
+        <v>420</v>
+      </c>
+      <c r="Z51" s="25" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="52" spans="1:26" ht="13.95" customHeight="1">
@@ -6054,7 +6587,7 @@
       <c r="P52" s="8">
         <v>175</v>
       </c>
-      <c r="Q52" s="17" t="s">
+      <c r="Q52" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R52" s="1" t="s">
@@ -6065,18 +6598,18 @@
       </c>
       <c r="T52" s="9"/>
       <c r="U52" s="9"/>
-      <c r="V52" s="19"/>
-      <c r="W52" s="20" t="s">
-        <v>472</v>
-      </c>
-      <c r="X52" s="25">
+      <c r="V52" s="18"/>
+      <c r="W52" s="19" t="s">
+        <v>470</v>
+      </c>
+      <c r="X52" s="24">
         <v>0</v>
       </c>
-      <c r="Y52" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="Z52" s="26" t="s">
-        <v>473</v>
+      <c r="Y52" s="25" t="s">
+        <v>420</v>
+      </c>
+      <c r="Z52" s="25" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="53" spans="1:26" ht="13.95" customHeight="1">
@@ -6126,7 +6659,7 @@
       <c r="P53" s="8">
         <v>120</v>
       </c>
-      <c r="Q53" s="17" t="s">
+      <c r="Q53" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R53" s="1" t="s">
@@ -6137,18 +6670,18 @@
       </c>
       <c r="T53" s="9"/>
       <c r="U53" s="9"/>
-      <c r="V53" s="19"/>
-      <c r="W53" s="20" t="s">
-        <v>474</v>
-      </c>
-      <c r="X53" s="25">
+      <c r="V53" s="18"/>
+      <c r="W53" s="19" t="s">
+        <v>472</v>
+      </c>
+      <c r="X53" s="24">
         <v>1</v>
       </c>
-      <c r="Y53" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="Z53" s="26" t="s">
-        <v>475</v>
+      <c r="Y53" s="25" t="s">
+        <v>420</v>
+      </c>
+      <c r="Z53" s="25" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="54" spans="1:26" ht="13.95" customHeight="1">
@@ -6198,7 +6731,7 @@
       <c r="P54" s="8">
         <v>35</v>
       </c>
-      <c r="Q54" s="17" t="s">
+      <c r="Q54" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R54" s="1" t="s">
@@ -6209,18 +6742,18 @@
       </c>
       <c r="T54" s="9"/>
       <c r="U54" s="9"/>
-      <c r="V54" s="19"/>
-      <c r="W54" s="20" t="s">
-        <v>476</v>
-      </c>
-      <c r="X54" s="25">
+      <c r="V54" s="18"/>
+      <c r="W54" s="19" t="s">
+        <v>474</v>
+      </c>
+      <c r="X54" s="24">
         <v>3</v>
       </c>
-      <c r="Y54" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="Z54" s="26" t="s">
-        <v>477</v>
+      <c r="Y54" s="25" t="s">
+        <v>420</v>
+      </c>
+      <c r="Z54" s="25" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="55" spans="1:26" ht="13.95" customHeight="1">
@@ -6270,7 +6803,7 @@
       <c r="P55" s="8">
         <v>28</v>
       </c>
-      <c r="Q55" s="17" t="s">
+      <c r="Q55" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R55" s="1" t="s">
@@ -6281,18 +6814,18 @@
       </c>
       <c r="T55" s="9"/>
       <c r="U55" s="9"/>
-      <c r="V55" s="19"/>
-      <c r="W55" s="20" t="s">
-        <v>478</v>
-      </c>
-      <c r="X55" s="25">
+      <c r="V55" s="18"/>
+      <c r="W55" s="19" t="s">
+        <v>476</v>
+      </c>
+      <c r="X55" s="24">
         <v>41</v>
       </c>
-      <c r="Y55" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="Z55" s="26" t="s">
-        <v>479</v>
+      <c r="Y55" s="25" t="s">
+        <v>420</v>
+      </c>
+      <c r="Z55" s="25" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="56" spans="1:26" ht="13.95" customHeight="1">
@@ -6342,7 +6875,7 @@
       <c r="P56" s="8">
         <v>110</v>
       </c>
-      <c r="Q56" s="17" t="s">
+      <c r="Q56" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R56" s="1" t="s">
@@ -6353,18 +6886,18 @@
       </c>
       <c r="T56" s="9"/>
       <c r="U56" s="9"/>
-      <c r="V56" s="19"/>
-      <c r="W56" s="20" t="s">
-        <v>480</v>
-      </c>
-      <c r="X56" s="25">
+      <c r="V56" s="18"/>
+      <c r="W56" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="X56" s="24">
         <v>350</v>
       </c>
-      <c r="Y56" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z56" s="26" t="s">
-        <v>481</v>
+      <c r="Y56" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z56" s="25" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="57" spans="1:26" ht="13.95" customHeight="1">
@@ -6414,7 +6947,7 @@
       <c r="P57" s="8">
         <v>60</v>
       </c>
-      <c r="Q57" s="17" t="s">
+      <c r="Q57" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R57" s="1" t="s">
@@ -6425,18 +6958,18 @@
       </c>
       <c r="T57" s="9"/>
       <c r="U57" s="9"/>
-      <c r="V57" s="19"/>
-      <c r="W57" s="20" t="s">
-        <v>482</v>
-      </c>
-      <c r="X57" s="25">
+      <c r="V57" s="18"/>
+      <c r="W57" s="19" t="s">
+        <v>480</v>
+      </c>
+      <c r="X57" s="24">
         <v>36</v>
       </c>
-      <c r="Y57" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="Z57" s="26" t="s">
-        <v>483</v>
+      <c r="Y57" s="25" t="s">
+        <v>420</v>
+      </c>
+      <c r="Z57" s="25" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="58" spans="1:26" ht="13.95" customHeight="1">
@@ -6486,7 +7019,7 @@
       <c r="P58" s="8">
         <v>120</v>
       </c>
-      <c r="Q58" s="17" t="s">
+      <c r="Q58" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R58" s="1" t="s">
@@ -6497,18 +7030,18 @@
       </c>
       <c r="T58" s="9"/>
       <c r="U58" s="9"/>
-      <c r="V58" s="19"/>
-      <c r="W58" s="20" t="s">
-        <v>484</v>
-      </c>
-      <c r="X58" s="25">
+      <c r="V58" s="18"/>
+      <c r="W58" s="19" t="s">
+        <v>482</v>
+      </c>
+      <c r="X58" s="24">
         <v>100</v>
       </c>
-      <c r="Y58" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z58" s="26" t="s">
-        <v>485</v>
+      <c r="Y58" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z58" s="25" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="59" spans="1:26" ht="13.95" customHeight="1">
@@ -6558,7 +7091,7 @@
       <c r="P59" s="8">
         <v>65</v>
       </c>
-      <c r="Q59" s="17" t="s">
+      <c r="Q59" s="16" t="s">
         <v>44</v>
       </c>
       <c r="R59" s="1" t="s">
@@ -6569,18 +7102,18 @@
       </c>
       <c r="T59" s="9"/>
       <c r="U59" s="9"/>
-      <c r="V59" s="19"/>
-      <c r="W59" s="20" t="s">
-        <v>486</v>
-      </c>
-      <c r="X59" s="25">
+      <c r="V59" s="18"/>
+      <c r="W59" s="19" t="s">
+        <v>484</v>
+      </c>
+      <c r="X59" s="24">
         <v>3</v>
       </c>
-      <c r="Y59" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="Z59" s="26" t="s">
-        <v>487</v>
+      <c r="Y59" s="25" t="s">
+        <v>420</v>
+      </c>
+      <c r="Z59" s="25" t="s">
+        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -7339,7 +7872,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="2.8984375" customWidth="1"/>
@@ -7360,12 +7893,11 @@
     <col min="16" max="16" width="13.8984375" customWidth="1"/>
     <col min="17" max="17" width="10.09765625" customWidth="1"/>
     <col min="18" max="18" width="12.8984375" customWidth="1"/>
-    <col min="19" max="19" width="13.19921875" customWidth="1"/>
-    <col min="20" max="20" width="35.59765625" customWidth="1"/>
-    <col min="21" max="21" width="8.19921875" customWidth="1"/>
+    <col min="19" max="19" width="35.59765625" customWidth="1"/>
+    <col min="20" max="20" width="8.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="19.2" customHeight="1">
+    <row r="1" spans="1:20" ht="19.2" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>17</v>
       </c>
@@ -7381,56 +7913,53 @@
       <c r="E1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="29" t="s">
         <v>292</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="29" t="s">
         <v>293</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="29" t="s">
         <v>294</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="29" t="s">
+        <v>486</v>
+      </c>
+      <c r="S1" s="29" t="s">
         <v>295</v>
       </c>
-      <c r="S1" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="U1" s="3" t="s">
+      <c r="T1" s="29" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="13.95" customHeight="1">
+    <row r="2" spans="1:20" ht="13.95" customHeight="1">
       <c r="A2" s="7"/>
       <c r="B2" s="1" t="s">
         <v>220</v>
@@ -7445,59 +7974,60 @@
         <f>IFERROR(INDEX(foods!$G:$G,MATCH(B2,foods!$B:$B,0)),"")</f>
         <v>2</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="F2" s="30" t="str">
         <f>IFERROR(INDEX(foods!$H:$H,MATCH(B2,foods!$B:$B,0)),"")</f>
         <v>COUNT</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="30">
         <f>IFERROR(INDEX(foods!$I:$I,MATCH(B2,foods!$B:$B,0)),"")</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="30">
         <f>IFERROR(INDEX(foods!$J:$J,MATCH(B2,foods!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="30">
         <f>IFERROR(INDEX(foods!$K:$K,MATCH(B2,foods!$B:$B,0)),"")</f>
         <v>13</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="30">
         <f>IFERROR(INDEX(foods!$L:$L,MATCH(B2,foods!$B:$B,0)),"")</f>
         <v>10</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="30">
         <f t="shared" ref="K2:K16" si="0">IF(OR(G2="",H2=""),"",MAX(G2-H2,0))</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="30">
         <f>IFERROR(INDEX(foods!$N:$N,MATCH(B2,foods!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="30">
         <f t="shared" ref="M2:M16" si="1">IF(OR(K2="",L2=""),"",K2*L2/100)</f>
         <v>0</v>
       </c>
-      <c r="N2" s="6">
+      <c r="N2" s="30">
         <f>IFERROR(INDEX(foods!$P:$P,MATCH(B2,foods!$B:$B,0)),"")</f>
         <v>150</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" s="31" t="s">
+        <v>296</v>
+      </c>
+      <c r="P2" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="34" t="s">
+        <v>489</v>
+      </c>
+      <c r="S2" s="32" t="s">
         <v>298</v>
       </c>
-      <c r="P2" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="12"/>
-      <c r="S2" s="12"/>
-      <c r="T2" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="U2" s="2" t="b">
+      <c r="T2" s="35" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="13.95" customHeight="1">
+    <row r="3" spans="1:20" ht="13.95" customHeight="1">
       <c r="A3" s="7"/>
       <c r="B3" s="1" t="s">
         <v>226</v>
@@ -7512,59 +8042,60 @@
         <f>IFERROR(INDEX(foods!$G:$G,MATCH(B3,foods!$B:$B,0)),"")</f>
         <v>1</v>
       </c>
-      <c r="F3" s="6" t="str">
+      <c r="F3" s="30" t="str">
         <f>IFERROR(INDEX(foods!$H:$H,MATCH(B3,foods!$B:$B,0)),"")</f>
         <v>COUNT</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="30">
         <f>IFERROR(INDEX(foods!$I:$I,MATCH(B3,foods!$B:$B,0)),"")</f>
         <v>5.7</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="30">
         <f>IFERROR(INDEX(foods!$J:$J,MATCH(B3,foods!$B:$B,0)),"")</f>
         <v>0.3</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="30">
         <f>IFERROR(INDEX(foods!$K:$K,MATCH(B3,foods!$B:$B,0)),"")</f>
         <v>4.66</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="30">
         <f>IFERROR(INDEX(foods!$L:$L,MATCH(B3,foods!$B:$B,0)),"")</f>
         <v>7.5</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="30">
         <f t="shared" si="0"/>
         <v>5.4</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="30">
         <f>IFERROR(INDEX(foods!$N:$N,MATCH(B3,foods!$B:$B,0)),"")</f>
         <v>15</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3" s="30">
         <f t="shared" si="1"/>
         <v>0.81</v>
       </c>
-      <c r="N3" s="6">
+      <c r="N3" s="30">
         <f>IFERROR(INDEX(foods!$P:$P,MATCH(B3,foods!$B:$B,0)),"")</f>
         <v>135</v>
       </c>
-      <c r="O3" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="P3" s="7" t="s">
+      <c r="O3" s="31" t="s">
+        <v>296</v>
+      </c>
+      <c r="P3" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q3" s="33"/>
+      <c r="R3" s="34" t="s">
+        <v>490</v>
+      </c>
+      <c r="S3" s="32" t="s">
         <v>299</v>
       </c>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="12"/>
-      <c r="S3" s="12"/>
-      <c r="T3" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="U3" s="2" t="b">
+      <c r="T3" s="35" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="13.95" customHeight="1">
+    <row r="4" spans="1:20" ht="13.95" customHeight="1">
       <c r="A4" s="7"/>
       <c r="B4" s="1" t="s">
         <v>229</v>
@@ -7579,59 +8110,60 @@
         <f>IFERROR(INDEX(foods!$G:$G,MATCH(B4,foods!$B:$B,0)),"")</f>
         <v>1</v>
       </c>
-      <c r="F4" s="6" t="str">
+      <c r="F4" s="30" t="str">
         <f>IFERROR(INDEX(foods!$H:$H,MATCH(B4,foods!$B:$B,0)),"")</f>
         <v>COUNT</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="30">
         <f>IFERROR(INDEX(foods!$I:$I,MATCH(B4,foods!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="30">
         <f>IFERROR(INDEX(foods!$J:$J,MATCH(B4,foods!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="30">
         <f>IFERROR(INDEX(foods!$K:$K,MATCH(B4,foods!$B:$B,0)),"")</f>
         <v>24</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="30">
         <f>IFERROR(INDEX(foods!$L:$L,MATCH(B4,foods!$B:$B,0)),"")</f>
         <v>2</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="30">
         <f>IFERROR(INDEX(foods!$N:$N,MATCH(B4,foods!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="30">
         <f>IFERROR(INDEX(foods!$P:$P,MATCH(B4,foods!$B:$B,0)),"")</f>
         <v>120</v>
       </c>
-      <c r="O4" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="P4" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="12"/>
-      <c r="S4" s="12"/>
-      <c r="T4" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="U4" s="2" t="b">
+      <c r="O4" s="31" t="s">
+        <v>296</v>
+      </c>
+      <c r="P4" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q4" s="33"/>
+      <c r="R4" s="34" t="s">
+        <v>491</v>
+      </c>
+      <c r="S4" s="32" t="s">
+        <v>300</v>
+      </c>
+      <c r="T4" s="35" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="13.95" customHeight="1">
+    <row r="5" spans="1:20" ht="13.95" customHeight="1">
       <c r="A5" s="7"/>
       <c r="B5" s="1" t="s">
         <v>231</v>
@@ -7646,59 +8178,60 @@
         <f>IFERROR(INDEX(foods!$G:$G,MATCH(B5,foods!$B:$B,0)),"")</f>
         <v>100</v>
       </c>
-      <c r="F5" s="6" t="str">
+      <c r="F5" s="30" t="str">
         <f>IFERROR(INDEX(foods!$H:$H,MATCH(B5,foods!$B:$B,0)),"")</f>
         <v>G</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="30">
         <f>IFERROR(INDEX(foods!$I:$I,MATCH(B5,foods!$B:$B,0)),"")</f>
         <v>5</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="30">
         <f>IFERROR(INDEX(foods!$J:$J,MATCH(B5,foods!$B:$B,0)),"")</f>
         <v>2.1</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="30">
         <f>IFERROR(INDEX(foods!$K:$K,MATCH(B5,foods!$B:$B,0)),"")</f>
         <v>1</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="30">
         <f>IFERROR(INDEX(foods!$L:$L,MATCH(B5,foods!$B:$B,0)),"")</f>
         <v>0.2</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="30">
         <f t="shared" si="0"/>
         <v>2.9</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="30">
         <f>IFERROR(INDEX(foods!$N:$N,MATCH(B5,foods!$B:$B,0)),"")</f>
         <v>15</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="30">
         <f t="shared" si="1"/>
         <v>0.435</v>
       </c>
-      <c r="N5" s="6">
+      <c r="N5" s="30">
         <f>IFERROR(INDEX(foods!$P:$P,MATCH(B5,foods!$B:$B,0)),"")</f>
         <v>20</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="O5" s="31" t="s">
+        <v>301</v>
+      </c>
+      <c r="P5" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q5" s="33"/>
+      <c r="R5" s="34" t="s">
+        <v>492</v>
+      </c>
+      <c r="S5" s="32" t="s">
         <v>303</v>
       </c>
-      <c r="P5" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="U5" s="2" t="b">
+      <c r="T5" s="35" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="13.95" customHeight="1">
+    <row r="6" spans="1:20" ht="13.95" customHeight="1">
       <c r="A6" s="7"/>
       <c r="B6" s="1" t="s">
         <v>233</v>
@@ -7713,59 +8246,60 @@
         <f>IFERROR(INDEX(foods!$G:$G,MATCH(B6,foods!$B:$B,0)),"")</f>
         <v>50</v>
       </c>
-      <c r="F6" s="6" t="str">
+      <c r="F6" s="30" t="str">
         <f>IFERROR(INDEX(foods!$H:$H,MATCH(B6,foods!$B:$B,0)),"")</f>
         <v>G</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="30">
         <f>IFERROR(INDEX(foods!$I:$I,MATCH(B6,foods!$B:$B,0)),"")</f>
         <v>2</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="30">
         <f>IFERROR(INDEX(foods!$J:$J,MATCH(B6,foods!$B:$B,0)),"")</f>
         <v>1.85</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="30">
         <f>IFERROR(INDEX(foods!$K:$K,MATCH(B6,foods!$B:$B,0)),"")</f>
         <v>1.25</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="30">
         <f>IFERROR(INDEX(foods!$L:$L,MATCH(B6,foods!$B:$B,0)),"")</f>
         <v>0.5</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="30">
         <f t="shared" si="0"/>
         <v>0.14999999999999991</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="30">
         <f>IFERROR(INDEX(foods!$N:$N,MATCH(B6,foods!$B:$B,0)),"")</f>
         <v>15</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="30">
         <f t="shared" si="1"/>
         <v>2.2499999999999985E-2</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="30">
         <f>IFERROR(INDEX(foods!$P:$P,MATCH(B6,foods!$B:$B,0)),"")</f>
         <v>15</v>
       </c>
-      <c r="O6" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="P6" s="7" t="s">
+      <c r="O6" s="31" t="s">
+        <v>301</v>
+      </c>
+      <c r="P6" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q6" s="33"/>
+      <c r="R6" s="34" t="s">
+        <v>489</v>
+      </c>
+      <c r="S6" s="32" t="s">
         <v>304</v>
       </c>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="12"/>
-      <c r="S6" s="12"/>
-      <c r="T6" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="U6" s="2" t="b">
+      <c r="T6" s="35" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="13.95" customHeight="1">
+    <row r="7" spans="1:20" ht="13.95" customHeight="1">
       <c r="A7" s="7"/>
       <c r="B7" s="1" t="s">
         <v>236</v>
@@ -7780,59 +8314,60 @@
         <f>IFERROR(INDEX(foods!$G:$G,MATCH(B7,foods!$B:$B,0)),"")</f>
         <v>200</v>
       </c>
-      <c r="F7" s="6" t="str">
+      <c r="F7" s="30" t="str">
         <f>IFERROR(INDEX(foods!$H:$H,MATCH(B7,foods!$B:$B,0)),"")</f>
         <v>G</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="30">
         <f>IFERROR(INDEX(foods!$I:$I,MATCH(B7,foods!$B:$B,0)),"")</f>
         <v>6</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="30">
         <f>IFERROR(INDEX(foods!$J:$J,MATCH(B7,foods!$B:$B,0)),"")</f>
         <v>1.6</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="30">
         <f>IFERROR(INDEX(foods!$K:$K,MATCH(B7,foods!$B:$B,0)),"")</f>
         <v>1.9</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="30">
         <f>IFERROR(INDEX(foods!$L:$L,MATCH(B7,foods!$B:$B,0)),"")</f>
         <v>0.2</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="30">
         <f t="shared" si="0"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="30">
         <f>IFERROR(INDEX(foods!$N:$N,MATCH(B7,foods!$B:$B,0)),"")</f>
         <v>15</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="30">
         <f t="shared" si="1"/>
         <v>0.66</v>
       </c>
-      <c r="N7" s="6">
+      <c r="N7" s="30">
         <f>IFERROR(INDEX(foods!$P:$P,MATCH(B7,foods!$B:$B,0)),"")</f>
         <v>25</v>
       </c>
-      <c r="O7" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="P7" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="12"/>
-      <c r="S7" s="12"/>
-      <c r="T7" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="U7" s="2" t="b">
+      <c r="O7" s="31" t="s">
+        <v>301</v>
+      </c>
+      <c r="P7" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q7" s="33"/>
+      <c r="R7" s="34" t="s">
+        <v>493</v>
+      </c>
+      <c r="S7" s="32" t="s">
+        <v>305</v>
+      </c>
+      <c r="T7" s="35" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="13.95" customHeight="1">
+    <row r="8" spans="1:20" ht="13.95" customHeight="1">
       <c r="A8" s="7"/>
       <c r="B8" s="1" t="s">
         <v>238</v>
@@ -7847,57 +8382,60 @@
         <f>IFERROR(INDEX(foods!$G:$G,MATCH(B8,foods!$B:$B,0)),"")</f>
         <v>100</v>
       </c>
-      <c r="F8" s="6" t="str">
+      <c r="F8" s="30" t="str">
         <f>IFERROR(INDEX(foods!$H:$H,MATCH(B8,foods!$B:$B,0)),"")</f>
         <v>G</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="30">
         <f>IFERROR(INDEX(foods!$I:$I,MATCH(B8,foods!$B:$B,0)),"")</f>
         <v>6</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="30">
         <f>IFERROR(INDEX(foods!$J:$J,MATCH(B8,foods!$B:$B,0)),"")</f>
         <v>2.5</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="30">
         <f>IFERROR(INDEX(foods!$K:$K,MATCH(B8,foods!$B:$B,0)),"")</f>
         <v>1.36</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="30">
         <f>IFERROR(INDEX(foods!$L:$L,MATCH(B8,foods!$B:$B,0)),"")</f>
         <v>0.1</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="30">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="30">
         <f>IFERROR(INDEX(foods!$N:$N,MATCH(B8,foods!$B:$B,0)),"")</f>
         <v>10</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="30">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="N8" s="6">
+      <c r="N8" s="30">
         <f>IFERROR(INDEX(foods!$P:$P,MATCH(B8,foods!$B:$B,0)),"")</f>
         <v>25</v>
       </c>
-      <c r="O8" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="P8" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="2" t="b">
+      <c r="O8" s="31" t="s">
+        <v>301</v>
+      </c>
+      <c r="P8" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q8" s="33"/>
+      <c r="R8" s="34" t="s">
+        <v>487</v>
+      </c>
+      <c r="S8" s="32" t="s">
+        <v>305</v>
+      </c>
+      <c r="T8" s="35" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="13.95" customHeight="1">
+    <row r="9" spans="1:20" ht="13.95" customHeight="1">
       <c r="A9" s="7"/>
       <c r="B9" s="1" t="s">
         <v>240</v>
@@ -7912,57 +8450,60 @@
         <f>IFERROR(INDEX(foods!$G:$G,MATCH(B9,foods!$B:$B,0)),"")</f>
         <v>30</v>
       </c>
-      <c r="F9" s="6" t="str">
+      <c r="F9" s="30" t="str">
         <f>IFERROR(INDEX(foods!$H:$H,MATCH(B9,foods!$B:$B,0)),"")</f>
         <v>G</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="30">
         <f>IFERROR(INDEX(foods!$I:$I,MATCH(B9,foods!$B:$B,0)),"")</f>
         <v>6.5</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="30">
         <f>IFERROR(INDEX(foods!$J:$J,MATCH(B9,foods!$B:$B,0)),"")</f>
         <v>3.39</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="30">
         <f>IFERROR(INDEX(foods!$K:$K,MATCH(B9,foods!$B:$B,0)),"")</f>
         <v>7.04</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="30">
         <f>IFERROR(INDEX(foods!$L:$L,MATCH(B9,foods!$B:$B,0)),"")</f>
         <v>15</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="30">
         <f t="shared" si="0"/>
         <v>3.11</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="30">
         <f>IFERROR(INDEX(foods!$N:$N,MATCH(B9,foods!$B:$B,0)),"")</f>
         <v>15</v>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="30">
         <f t="shared" si="1"/>
         <v>0.46649999999999997</v>
       </c>
-      <c r="N9" s="6">
+      <c r="N9" s="30">
         <f>IFERROR(INDEX(foods!$P:$P,MATCH(B9,foods!$B:$B,0)),"")</f>
         <v>175</v>
       </c>
-      <c r="O9" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="P9" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q9" s="10"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="2" t="b">
+      <c r="O9" s="31" t="s">
+        <v>306</v>
+      </c>
+      <c r="P9" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q9" s="33"/>
+      <c r="R9" s="34" t="s">
+        <v>493</v>
+      </c>
+      <c r="S9" s="32" t="s">
+        <v>303</v>
+      </c>
+      <c r="T9" s="35" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="13.95" customHeight="1">
+    <row r="10" spans="1:20" ht="13.95" customHeight="1">
       <c r="A10" s="7"/>
       <c r="B10" s="1" t="s">
         <v>243</v>
@@ -7977,57 +8518,60 @@
         <f>IFERROR(INDEX(foods!$G:$G,MATCH(B10,foods!$B:$B,0)),"")</f>
         <v>1</v>
       </c>
-      <c r="F10" s="6" t="str">
+      <c r="F10" s="30" t="str">
         <f>IFERROR(INDEX(foods!$H:$H,MATCH(B10,foods!$B:$B,0)),"")</f>
         <v>COUNT</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="30">
         <f>IFERROR(INDEX(foods!$I:$I,MATCH(B10,foods!$B:$B,0)),"")</f>
         <v>35</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="30">
         <f>IFERROR(INDEX(foods!$J:$J,MATCH(B10,foods!$B:$B,0)),"")</f>
         <v>3.6</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="30">
         <f>IFERROR(INDEX(foods!$K:$K,MATCH(B10,foods!$B:$B,0)),"")</f>
         <v>0.52</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="30">
         <f>IFERROR(INDEX(foods!$L:$L,MATCH(B10,foods!$B:$B,0)),"")</f>
         <v>0.3</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="30">
         <f t="shared" si="0"/>
         <v>31.4</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="30">
         <f>IFERROR(INDEX(foods!$N:$N,MATCH(B10,foods!$B:$B,0)),"")</f>
         <v>36</v>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="30">
         <f t="shared" si="1"/>
         <v>11.303999999999998</v>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="30">
         <f>IFERROR(INDEX(foods!$P:$P,MATCH(B10,foods!$B:$B,0)),"")</f>
         <v>120</v>
       </c>
-      <c r="O10" s="1" t="s">
+      <c r="O10" s="31" t="s">
+        <v>301</v>
+      </c>
+      <c r="P10" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q10" s="33"/>
+      <c r="R10" s="34" t="s">
+        <v>491</v>
+      </c>
+      <c r="S10" s="32" t="s">
         <v>303</v>
       </c>
-      <c r="P10" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
-      <c r="T10" s="7"/>
-      <c r="U10" s="2" t="b">
+      <c r="T10" s="35" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="13.95" customHeight="1">
+    <row r="11" spans="1:20" ht="13.95" customHeight="1">
       <c r="A11" s="7"/>
       <c r="B11" s="1" t="s">
         <v>245</v>
@@ -8042,57 +8586,60 @@
         <f>IFERROR(INDEX(foods!$G:$G,MATCH(B11,foods!$B:$B,0)),"")</f>
         <v>1</v>
       </c>
-      <c r="F11" s="6" t="str">
+      <c r="F11" s="30" t="str">
         <f>IFERROR(INDEX(foods!$H:$H,MATCH(B11,foods!$B:$B,0)),"")</f>
         <v>COUNT</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="30">
         <f>IFERROR(INDEX(foods!$I:$I,MATCH(B11,foods!$B:$B,0)),"")</f>
         <v>9</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="30">
         <f>IFERROR(INDEX(foods!$J:$J,MATCH(B11,foods!$B:$B,0)),"")</f>
         <v>1.6</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="30">
         <f>IFERROR(INDEX(foods!$K:$K,MATCH(B11,foods!$B:$B,0)),"")</f>
         <v>0.91</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="30">
         <f>IFERROR(INDEX(foods!$L:$L,MATCH(B11,foods!$B:$B,0)),"")</f>
         <v>0.3</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="30">
         <f t="shared" si="0"/>
         <v>7.4</v>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="30">
         <f>IFERROR(INDEX(foods!$N:$N,MATCH(B11,foods!$B:$B,0)),"")</f>
         <v>15</v>
       </c>
-      <c r="M11" s="6">
+      <c r="M11" s="30">
         <f t="shared" si="1"/>
         <v>1.1100000000000001</v>
       </c>
-      <c r="N11" s="6">
+      <c r="N11" s="30">
         <f>IFERROR(INDEX(foods!$P:$P,MATCH(B11,foods!$B:$B,0)),"")</f>
         <v>35</v>
       </c>
-      <c r="O11" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="P11" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
-      <c r="T11" s="7"/>
-      <c r="U11" s="2" t="b">
+      <c r="O11" s="31" t="s">
+        <v>301</v>
+      </c>
+      <c r="P11" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q11" s="33"/>
+      <c r="R11" s="34" t="s">
+        <v>494</v>
+      </c>
+      <c r="S11" s="32" t="s">
+        <v>305</v>
+      </c>
+      <c r="T11" s="35" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="13.95" customHeight="1">
+    <row r="12" spans="1:20" ht="13.95" customHeight="1">
       <c r="A12" s="7"/>
       <c r="B12" s="1" t="s">
         <v>247</v>
@@ -8107,57 +8654,60 @@
         <f>IFERROR(INDEX(foods!$G:$G,MATCH(B12,foods!$B:$B,0)),"")</f>
         <v>1</v>
       </c>
-      <c r="F12" s="6" t="str">
+      <c r="F12" s="30" t="str">
         <f>IFERROR(INDEX(foods!$H:$H,MATCH(B12,foods!$B:$B,0)),"")</f>
         <v>COUNT</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="30">
         <f>IFERROR(INDEX(foods!$I:$I,MATCH(B12,foods!$B:$B,0)),"")</f>
         <v>5.34</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="30">
         <f>IFERROR(INDEX(foods!$J:$J,MATCH(B12,foods!$B:$B,0)),"")</f>
         <v>3.1</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="30">
         <f>IFERROR(INDEX(foods!$K:$K,MATCH(B12,foods!$B:$B,0)),"")</f>
         <v>2.8</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="30">
         <f>IFERROR(INDEX(foods!$L:$L,MATCH(B12,foods!$B:$B,0)),"")</f>
         <v>0.31</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="30">
         <f t="shared" si="0"/>
         <v>2.2399999999999998</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="30">
         <f>IFERROR(INDEX(foods!$N:$N,MATCH(B12,foods!$B:$B,0)),"")</f>
         <v>10</v>
       </c>
-      <c r="M12" s="6">
+      <c r="M12" s="30">
         <f t="shared" si="1"/>
         <v>0.22399999999999998</v>
       </c>
-      <c r="N12" s="6">
+      <c r="N12" s="30">
         <f>IFERROR(INDEX(foods!$P:$P,MATCH(B12,foods!$B:$B,0)),"")</f>
         <v>28</v>
       </c>
-      <c r="O12" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="P12" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q12" s="10"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
-      <c r="T12" s="7"/>
-      <c r="U12" s="2" t="b">
+      <c r="O12" s="31" t="s">
+        <v>301</v>
+      </c>
+      <c r="P12" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q12" s="33"/>
+      <c r="R12" s="34" t="s">
+        <v>490</v>
+      </c>
+      <c r="S12" s="32" t="s">
+        <v>305</v>
+      </c>
+      <c r="T12" s="35" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="13.95" customHeight="1">
+    <row r="13" spans="1:20" ht="13.95" customHeight="1">
       <c r="A13" s="7"/>
       <c r="B13" s="1" t="s">
         <v>249</v>
@@ -8172,57 +8722,60 @@
         <f>IFERROR(INDEX(foods!$G:$G,MATCH(B13,foods!$B:$B,0)),"")</f>
         <v>1</v>
       </c>
-      <c r="F13" s="6" t="str">
+      <c r="F13" s="30" t="str">
         <f>IFERROR(INDEX(foods!$H:$H,MATCH(B13,foods!$B:$B,0)),"")</f>
         <v>COUNT</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="30">
         <f>IFERROR(INDEX(foods!$I:$I,MATCH(B13,foods!$B:$B,0)),"")</f>
         <v>1</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="30">
         <f>IFERROR(INDEX(foods!$J:$J,MATCH(B13,foods!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="30">
         <f>IFERROR(INDEX(foods!$K:$K,MATCH(B13,foods!$B:$B,0)),"")</f>
         <v>19</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="30">
         <f>IFERROR(INDEX(foods!$L:$L,MATCH(B13,foods!$B:$B,0)),"")</f>
         <v>5</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="30">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="30">
         <f>IFERROR(INDEX(foods!$N:$N,MATCH(B13,foods!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M13" s="6">
+      <c r="M13" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N13" s="6">
+      <c r="N13" s="30">
         <f>IFERROR(INDEX(foods!$P:$P,MATCH(B13,foods!$B:$B,0)),"")</f>
         <v>110</v>
       </c>
-      <c r="O13" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="P13" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="12"/>
-      <c r="S13" s="12"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="2" t="b">
+      <c r="O13" s="31" t="s">
+        <v>296</v>
+      </c>
+      <c r="P13" s="32" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q13" s="33"/>
+      <c r="R13" s="34" t="s">
+        <v>494</v>
+      </c>
+      <c r="S13" s="32" t="s">
+        <v>300</v>
+      </c>
+      <c r="T13" s="35" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="13.95" customHeight="1">
+    <row r="14" spans="1:20" ht="13.95" customHeight="1">
       <c r="A14" s="7"/>
       <c r="B14" s="1" t="s">
         <v>251</v>
@@ -8237,57 +8790,60 @@
         <f>IFERROR(INDEX(foods!$G:$G,MATCH(B14,foods!$B:$B,0)),"")</f>
         <v>100</v>
       </c>
-      <c r="F14" s="6" t="str">
+      <c r="F14" s="30" t="str">
         <f>IFERROR(INDEX(foods!$H:$H,MATCH(B14,foods!$B:$B,0)),"")</f>
         <v>G</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="30">
         <f>IFERROR(INDEX(foods!$I:$I,MATCH(B14,foods!$B:$B,0)),"")</f>
         <v>4</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="30">
         <f>IFERROR(INDEX(foods!$J:$J,MATCH(B14,foods!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="30">
         <f>IFERROR(INDEX(foods!$K:$K,MATCH(B14,foods!$B:$B,0)),"")</f>
         <v>7.33</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="30">
         <f>IFERROR(INDEX(foods!$L:$L,MATCH(B14,foods!$B:$B,0)),"")</f>
         <v>2</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="30">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="30">
         <f>IFERROR(INDEX(foods!$N:$N,MATCH(B14,foods!$B:$B,0)),"")</f>
         <v>17</v>
       </c>
-      <c r="M14" s="6">
+      <c r="M14" s="30">
         <f t="shared" si="1"/>
         <v>0.68</v>
       </c>
-      <c r="N14" s="6">
+      <c r="N14" s="30">
         <f>IFERROR(INDEX(foods!$P:$P,MATCH(B14,foods!$B:$B,0)),"")</f>
         <v>60</v>
       </c>
-      <c r="O14" s="1" t="s">
+      <c r="O14" s="31" t="s">
+        <v>296</v>
+      </c>
+      <c r="P14" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q14" s="33"/>
+      <c r="R14" s="34" t="s">
+        <v>495</v>
+      </c>
+      <c r="S14" s="32" t="s">
         <v>298</v>
       </c>
-      <c r="P14" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="12"/>
-      <c r="S14" s="12"/>
-      <c r="T14" s="7"/>
-      <c r="U14" s="2" t="b">
+      <c r="T14" s="35" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="13.95" customHeight="1">
+    <row r="15" spans="1:20" ht="13.95" customHeight="1">
       <c r="A15" s="7"/>
       <c r="B15" s="1" t="s">
         <v>253</v>
@@ -8302,57 +8858,60 @@
         <f>IFERROR(INDEX(foods!$G:$G,MATCH(B15,foods!$B:$B,0)),"")</f>
         <v>200</v>
       </c>
-      <c r="F15" s="6" t="str">
+      <c r="F15" s="30" t="str">
         <f>IFERROR(INDEX(foods!$H:$H,MATCH(B15,foods!$B:$B,0)),"")</f>
         <v>ML</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="30">
         <f>IFERROR(INDEX(foods!$I:$I,MATCH(B15,foods!$B:$B,0)),"")</f>
         <v>9</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="30">
         <f>IFERROR(INDEX(foods!$J:$J,MATCH(B15,foods!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="30">
         <f>IFERROR(INDEX(foods!$K:$K,MATCH(B15,foods!$B:$B,0)),"")</f>
         <v>6</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="30">
         <f>IFERROR(INDEX(foods!$L:$L,MATCH(B15,foods!$B:$B,0)),"")</f>
         <v>6</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="30">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="30">
         <f>IFERROR(INDEX(foods!$N:$N,MATCH(B15,foods!$B:$B,0)),"")</f>
         <v>27</v>
       </c>
-      <c r="M15" s="6">
+      <c r="M15" s="30">
         <f t="shared" si="1"/>
         <v>2.4300000000000002</v>
       </c>
-      <c r="N15" s="6">
+      <c r="N15" s="30">
         <f>IFERROR(INDEX(foods!$P:$P,MATCH(B15,foods!$B:$B,0)),"")</f>
         <v>120</v>
       </c>
-      <c r="O15" s="1" t="s">
+      <c r="O15" s="31" t="s">
+        <v>296</v>
+      </c>
+      <c r="P15" s="32" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q15" s="33"/>
+      <c r="R15" s="34" t="s">
+        <v>496</v>
+      </c>
+      <c r="S15" s="32" t="s">
         <v>298</v>
       </c>
-      <c r="P15" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="12"/>
-      <c r="S15" s="12"/>
-      <c r="T15" s="7"/>
-      <c r="U15" s="2" t="b">
+      <c r="T15" s="35" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="13.95" customHeight="1">
+    <row r="16" spans="1:20" ht="13.95" customHeight="1">
       <c r="A16" s="7"/>
       <c r="B16" s="1" t="s">
         <v>256</v>
@@ -8367,53 +8926,56 @@
         <f>IFERROR(INDEX(foods!$G:$G,MATCH(B16,foods!$B:$B,0)),"")</f>
         <v>50</v>
       </c>
-      <c r="F16" s="6" t="str">
+      <c r="F16" s="30" t="str">
         <f>IFERROR(INDEX(foods!$H:$H,MATCH(B16,foods!$B:$B,0)),"")</f>
         <v>G</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="30">
         <f>IFERROR(INDEX(foods!$I:$I,MATCH(B16,foods!$B:$B,0)),"")</f>
         <v>5</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H16" s="30">
         <f>IFERROR(INDEX(foods!$J:$J,MATCH(B16,foods!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="30">
         <f>IFERROR(INDEX(foods!$K:$K,MATCH(B16,foods!$B:$B,0)),"")</f>
         <v>6</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J16" s="30">
         <f>IFERROR(INDEX(foods!$L:$L,MATCH(B16,foods!$B:$B,0)),"")</f>
         <v>3</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="30">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L16" s="6">
+      <c r="L16" s="30">
         <f>IFERROR(INDEX(foods!$N:$N,MATCH(B16,foods!$B:$B,0)),"")</f>
         <v>18</v>
       </c>
-      <c r="M16" s="6">
+      <c r="M16" s="30">
         <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
-      <c r="N16" s="6">
+      <c r="N16" s="30">
         <f>IFERROR(INDEX(foods!$P:$P,MATCH(B16,foods!$B:$B,0)),"")</f>
         <v>65</v>
       </c>
-      <c r="O16" s="1" t="s">
+      <c r="O16" s="31" t="s">
+        <v>296</v>
+      </c>
+      <c r="P16" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q16" s="33"/>
+      <c r="R16" s="34" t="s">
+        <v>488</v>
+      </c>
+      <c r="S16" s="32" t="s">
         <v>298</v>
       </c>
-      <c r="P16" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q16" s="10"/>
-      <c r="R16" s="12"/>
-      <c r="S16" s="12"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="2" t="b">
+      <c r="T16" s="35" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8427,7 +8989,7 @@
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
-    <dataValidation type="list" sqref="U2:U16" xr:uid="{00000000-0002-0000-0400-000002000000}">
+    <dataValidation type="list" sqref="T2:T16" xr:uid="{00000000-0002-0000-0400-000002000000}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8453,322 +9015,322 @@
   <sheetData>
     <row r="1" spans="1:6" ht="19.2" customHeight="1">
       <c r="A1" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>313</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="13.95" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="13.95" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="13.95" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="13.95" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="13.95" customHeight="1">
       <c r="A6" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="E6" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="13.95" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="13.95" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="13.95" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="13.95" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="13.95" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>258</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="13.95" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>287</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="13.95" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>292</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="13.95" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="13.95" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>294</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="13.95" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>
